--- a/menu.xlsx
+++ b/menu.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUTOSH PASTOR\Desktop\mess\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUTOSH PASTOR\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2741B62-F85B-4AE9-B638-5BA7EFE522D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{69D9DE51-2716-4B9C-A25D-32E068E15BEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2616" yWindow="2616" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table 2" sheetId="2" r:id="rId1"/>
@@ -463,20 +463,20 @@
     <t>Monday</t>
   </si>
   <si>
-    <t>SNACKS 4:30 PM TO 5:30 PM</t>
-  </si>
-  <si>
-    <t>DINNER 8:15 PM TO 8:50 PM</t>
-  </si>
-  <si>
     <t>Roti, Paneer ki sabji(PaneerdoPyaja, Matar Paneer, Butter Paneer, Paneer masala,Sahi
 Paneer),TourDalfry,Sweet</t>
   </si>
   <si>
-    <t>LUNCH 12:30 PM TO 1:30 PM</t>
-  </si>
-  <si>
-    <t>BREAKFAST 8:00 AM TO 8:50 AM</t>
+    <t>BREAKFAST 2:30 AM TO 3:30 AM</t>
+  </si>
+  <si>
+    <t>DINNER 2:45 PM TO 3:30 PM</t>
+  </si>
+  <si>
+    <t>SNACKS 11:00 AM TO 12:00 PM</t>
+  </si>
+  <si>
+    <t>LUNCH 7:00 AM TO 8:00 AM</t>
   </si>
 </sst>
 </file>
@@ -1120,7 +1120,7 @@
     </row>
     <row r="2" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="29" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B2" s="30"/>
       <c r="C2" s="4" t="s">
@@ -1147,7 +1147,7 @@
     </row>
     <row r="3" spans="1:9" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="31" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B3" s="32"/>
       <c r="C3" s="7" t="s">
@@ -1189,7 +1189,7 @@
     </row>
     <row r="5" spans="1:9" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="29" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B5" s="30"/>
       <c r="C5" s="4" t="s">
@@ -1216,7 +1216,7 @@
     </row>
     <row r="6" spans="1:9" ht="91.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="33" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B6" s="34"/>
       <c r="C6" s="19" t="s">
@@ -1238,7 +1238,7 @@
         <v>33</v>
       </c>
       <c r="I6" s="18" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="31.05" customHeight="1" x14ac:dyDescent="0.25">

--- a/menu.xlsx
+++ b/menu.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUTOSH PASTOR\Desktop\mess\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8FB37806-9B34-4EA0-B5FF-9444800BF8AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30811497-662D-481E-A038-FFD20F584D6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -150,16 +150,16 @@
 OR Biscuit, Tea</t>
   </si>
   <si>
-    <t>Roti, Paneer ki Sabji (Paneer do Pyaja, Matar Paneer, Butter Paneer, Paneer Masala, Shahi Paneer), Tuar Dal Fry, Sweets (Gulab Jamun, Seviya Kheer), Jeera Rice, Salad, Aachar
-OR Veg Biryani, Chach, Aachar
-OR Butter Khichdi, Papad, Aachar
-OR Rice, Tuar Daal, Aachar, Salad</t>
-  </si>
-  <si>
-    <t>Tea</t>
-  </si>
-  <si>
-    <t>Dal Bafla, Tomato Chutney</t>
+    <t>Roti, Paneer ki Sabji , Tuar Dal Fry, Sweets , Jeera Rice, Salad, Aachar
+OR                   Veg Biryani, Chach, Aachar
+OR                 Butter Khichdi, Papad, Aachar
+OR                 Rice, Tuar Daal, Aachar, Salad           OR                         dal bafle , tomato chutny</t>
+  </si>
+  <si>
+    <t xml:space="preserve">toast tea or  biscuit , tea </t>
+  </si>
+  <si>
+    <t>veg briyani , chach aachar              or                butter khichdi , papad aachar                  or                 rice,tuar daal , aachar , salad</t>
   </si>
 </sst>
 </file>

--- a/menu.xlsx
+++ b/menu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUTOSH PASTOR\Desktop\mess\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30811497-662D-481E-A038-FFD20F584D6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11296781-2380-46D9-87BC-E4DF50E45588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -150,16 +150,14 @@
 OR Biscuit, Tea</t>
   </si>
   <si>
+    <t xml:space="preserve">toast tea or  biscuit , tea </t>
+  </si>
+  <si>
     <t>Roti, Paneer ki Sabji , Tuar Dal Fry, Sweets , Jeera Rice, Salad, Aachar
-OR                   Veg Biryani, Chach, Aachar
-OR                 Butter Khichdi, Papad, Aachar
-OR                 Rice, Tuar Daal, Aachar, Salad           OR                         dal bafle , tomato chutny</t>
-  </si>
-  <si>
-    <t xml:space="preserve">toast tea or  biscuit , tea </t>
-  </si>
-  <si>
-    <t>veg briyani , chach aachar              or                butter khichdi , papad aachar                  or                 rice,tuar daal , aachar , salad</t>
+OR                                                                                           dal bafle , tomato chutny</t>
+  </si>
+  <si>
+    <t>veg briyani , chach aachar  OR   butter khichdi , papad aachar   OR   rice,tuar daal , aachar , salad</t>
   </si>
 </sst>
 </file>
@@ -742,10 +740,10 @@
         <v>41</v>
       </c>
       <c r="C9" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>43</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>44</v>
